--- a/docassemble/MAEvictionDefense/data/sources/eviction_zh-t.xlsx
+++ b/docassemble/MAEvictionDefense/data/sources/eviction_zh-t.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1220"/>
+  <dimension ref="A1:H1224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25.7109375" customWidth="1" min="1" max="1"/>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>06affba7ad2203d850a91c6af6819f61</t>
+          <t>575ad08957cfe9bd85d7f94d8711ed35</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
@@ -18268,7 +18268,7 @@
           <t xml:space="preserve">You can continue this interview on another device, or share it with 
 someone who will help you finish it. Choose any of the options below to share
 the interview.
-Right-click and copy [this link](${interview_url()}).
+Right-click and copy [the link to your interview](${interview_url()}).
 % if device() and not device().is_mobile:
 Use your phone's camera to point at this barcode. Click the link that appears
 in the camera's viewfinder.
@@ -18284,7 +18284,7 @@
           <t xml:space="preserve">您可以在另一台設備繼續進行本次訪談，或向他人分享，
 以便他人替您完成訪談。選擇以下任意選項，
 分享訪談。
-按下滑鼠右鍵，並複製[本連結](${interview_url()})。
+按下滑鼠右鍵，並複製[您的訪談連結](${interview_url()})。
 % if device() and not device().is_mobile: 
 使用行動電話的攝像頭掃描本條碼。點選攝像頭觀景器中
 出現的連結。
@@ -40572,7 +40572,7 @@
       </c>
       <c r="D949" s="2" t="inlineStr">
         <is>
-          <t>405a7c1de4db0b51f49baacb5de85580</t>
+          <t>8d80904edef43f2eedc35a288289b349</t>
         </is>
       </c>
       <c r="E949" s="2" t="inlineStr">
@@ -40602,7 +40602,7 @@
   ${landlord.name}.
 % endif
 You also need to send a copy of the motion to ${court}.
-Learn more and continue the form online [here](${interview_url()}) or download
+Learn more and [continue the form online](${interview_url()}) or download
 the PDF here: https://gbls.org/tactics/compel.
 </t>
         </is>
@@ -40623,7 +40623,7 @@
   ${landlord.name}。
 % endif
 您還需要向 ${court}發送一份申請副本。
-瞭解更多，或繼續填寫線上表格[此處](${interview_url()})，或者，從此處下載PDF：https://gbls.org/tactics/compel 。
+瞭解更多，或[繼續填寫線上表格](${interview_url()})，或者，從此處下載PDF：https://gbls.org/tactics/compel 。
 </t>
         </is>
       </c>
@@ -40902,7 +40902,7 @@
       </c>
       <c r="D955" s="2" t="inlineStr">
         <is>
-          <t>26fd8aed4ec30f78c45f916032146cd5</t>
+          <t>cec6553a0281b8bd2f9e4a1f35f60906</t>
         </is>
       </c>
       <c r="E955" s="2" t="inlineStr">
@@ -40919,7 +40919,7 @@
         <is>
           <t xml:space="preserve">Someone who was completing an interview using Massachusetts Defense for
 Eviction (MADE) sent you this link.
-Click [here](${interview_url()}) to keep working on the interview.
+[Keep working on the interview](${interview_url()}).
 </t>
         </is>
       </c>
@@ -40927,7 +40927,7 @@
         <is>
           <t xml:space="preserve">之前使用麻薩諸塞州驅離抗辯 (MADE) 進行訪談的人
 向您發送了此連結。
-點選 [此處](${interview_url()}) 繼續訪談。
+[繼續進行訪談](${interview_url()})。
 </t>
         </is>
       </c>
@@ -53259,6 +53259,207 @@
         </is>
       </c>
     </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1221" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>a2beb488f5408ec32ba0f33f24c6c5e1</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>zh-t</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>By hand</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>親手交付</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1222" t="n">
+        <v>13</v>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>dfc27ef27b631b0e7114573a439c3180</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>zh-t</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>By email</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>透過電子郵件</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1223" t="n">
+        <v>14</v>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>409b1ef3ad4fe98ad063fb3026c6b250</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>zh-t</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>By mail</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>郵寄</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>docassemble.MAEvictionDefense:data/questions/eviction.en.yml</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>method of service</t>
+        </is>
+      </c>
+      <c r="C1224" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>966afd80841437ca4adfcf8f54bfab2a</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>zh-t</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">You must give a copy of the forms we are working on to your landlord or their 
+attorney. 
+% if case.hearing_date_assigned:
+They need to _get_ the forms no later than 
+**${format_date(case.answer_date)}**.
+% if answer_date_is_holiday:
+Because ${case.answer_date} is ${answer_date_holiday}, you can
+deliver it the next weekday after ${answer_date_holiday}.
+% endif
+% else:
+Give a copy to your landlord or their attorney as soon as you can.
+% endif
+Deliver it in person
+if you can. If your landlord has a lawyer, you can email it to the lawyer.
+If your landlord does not have a lawyer, ask them first before you email it. 
+% if format_date(case.answer_date) == format_date(today()):
+It's too late to mail the paperwork.
+% else:
+Only mail it if you know
+your landlord will get it on or before ${format_date(case.answer_date)}.
+% endif
+</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">您必須把我們正在處理的表格副本交給您的房東或其律師。
+% if case.hearing_date_assigned:
+他們必須在 
+**${format_date(case.answer_date)}** 之前_收到_這些表格。
+% if answer_date_is_holiday:
+由於 ${case.answer_date} 是 ${answer_date_holiday}，您可以在
+${answer_date_holiday} 之後的下一個工作日交付。
+% endif
+% else:
+請盡快將副本交給您的房東或其律師。
+% endif
+如果可以，請
+親自交付。如果您的房東有律師，您可以用電子郵件寄給該律師。
+如果您的房東沒有律師，請先徵得他們同意再用電子郵件寄送。 
+% if format_date(case.answer_date) == format_date(today()):
+現在郵寄文件已經太遲了。
+% else:
+只有在您確定房東會在 ${format_date(case.answer_date)} 當天或之前收到時，
+才用郵寄。
+% endif
+</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
